--- a/Structure and plan info/Plan Info.xlsx
+++ b/Structure and plan info/Plan Info.xlsx
@@ -765,26 +765,29 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100015C8FEAEB314B4A9749EFED9CE4B8B6" ma:contentTypeVersion="10" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="e076aaec7a08db0dda782f1a791b9a37">
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns3="7183ed49-9f5f-4b04-a53a-40b3f7491946" xmlns:ns4="dcf9c071-f24f-474f-b8f2-caf1c44d8fe8" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="9c2d71bd8a9146118350562cf545912f" ns3:_="" ns4:_="">
-    <xsd:import namespace="7183ed49-9f5f-4b04-a53a-40b3f7491946"/>
-    <xsd:import namespace="dcf9c071-f24f-474f-b8f2-caf1c44d8fe8"/>
+<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101003F5ED4C9C3BCF64FB602E6BC73E05343" ma:contentTypeVersion="14" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="b589f7e5eeb6bec19614f33cf7f0cf85">
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="347c6671-e14e-499f-bdff-5abebf9f2841" xmlns:ns3="ad65eebb-9aa8-49dc-954e-2f274fb67fdf" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="7942d335befb87718259710f93a11325" ns2:_="" ns3:_="">
+    <xsd:import namespace="347c6671-e14e-499f-bdff-5abebf9f2841"/>
+    <xsd:import namespace="ad65eebb-9aa8-49dc-954e-2f274fb67fdf"/>
     <xsd:element name="properties">
       <xsd:complexType>
         <xsd:sequence>
           <xsd:element name="documentManagement">
             <xsd:complexType>
               <xsd:all>
+                <xsd:element ref="ns2:MediaServiceMetadata" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceFastMetadata" minOccurs="0"/>
+                <xsd:element ref="ns2:lcf76f155ced4ddcb4097134ff3c332f" minOccurs="0"/>
+                <xsd:element ref="ns3:TaxCatchAll" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceOCR" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceGenerationTime" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceEventHashCode" minOccurs="0"/>
                 <xsd:element ref="ns3:SharedWithUsers" minOccurs="0"/>
-                <xsd:element ref="ns3:SharingHintHash" minOccurs="0"/>
                 <xsd:element ref="ns3:SharedWithDetails" minOccurs="0"/>
-                <xsd:element ref="ns4:MediaServiceMetadata" minOccurs="0"/>
-                <xsd:element ref="ns4:MediaServiceFastMetadata" minOccurs="0"/>
-                <xsd:element ref="ns4:MediaServiceAutoTags" minOccurs="0"/>
-                <xsd:element ref="ns4:MediaServiceOCR" minOccurs="0"/>
-                <xsd:element ref="ns4:MediaServiceDateTaken" minOccurs="0"/>
-                <xsd:element ref="ns4:MediaServiceEventHashCode" minOccurs="0"/>
-                <xsd:element ref="ns4:MediaServiceGenerationTime" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceObjectDetectorVersions" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceDateTaken" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaLengthInSeconds" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceSearchProperties" minOccurs="0"/>
               </xsd:all>
             </xsd:complexType>
           </xsd:element>
@@ -792,10 +795,79 @@
       </xsd:complexType>
     </xsd:element>
   </xsd:schema>
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="7183ed49-9f5f-4b04-a53a-40b3f7491946" elementFormDefault="qualified">
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="347c6671-e14e-499f-bdff-5abebf9f2841" elementFormDefault="qualified">
     <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
     <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <xsd:element name="SharedWithUsers" ma:index="8" nillable="true" ma:displayName="Shared With" ma:internalName="SharedWithUsers" ma:readOnly="true">
+    <xsd:element name="MediaServiceMetadata" ma:index="8" nillable="true" ma:displayName="MediaServiceMetadata" ma:hidden="true" ma:internalName="MediaServiceMetadata" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceFastMetadata" ma:index="9" nillable="true" ma:displayName="MediaServiceFastMetadata" ma:hidden="true" ma:internalName="MediaServiceFastMetadata" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="lcf76f155ced4ddcb4097134ff3c332f" ma:index="11" nillable="true" ma:taxonomy="true" ma:internalName="lcf76f155ced4ddcb4097134ff3c332f" ma:taxonomyFieldName="MediaServiceImageTags" ma:displayName="Image Tags" ma:readOnly="false" ma:fieldId="{5cf76f15-5ced-4ddc-b409-7134ff3c332f}" ma:taxonomyMulti="true" ma:sspId="92cb0cb5-3640-4022-b6af-d60faf1e35e8" ma:termSetId="09814cd3-568e-fe90-9814-8d621ff8fb84" ma:anchorId="fba54fb3-c3e1-fe81-a776-ca4b69148c4d" ma:open="true" ma:isKeyword="false">
+      <xsd:complexType>
+        <xsd:sequence>
+          <xsd:element ref="pc:Terms" minOccurs="0" maxOccurs="1"/>
+        </xsd:sequence>
+      </xsd:complexType>
+    </xsd:element>
+    <xsd:element name="MediaServiceOCR" ma:index="13" nillable="true" ma:displayName="Extracted Text" ma:internalName="MediaServiceOCR" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note">
+          <xsd:maxLength value="255"/>
+        </xsd:restriction>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceGenerationTime" ma:index="14" nillable="true" ma:displayName="MediaServiceGenerationTime" ma:hidden="true" ma:internalName="MediaServiceGenerationTime" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceEventHashCode" ma:index="15" nillable="true" ma:displayName="MediaServiceEventHashCode" ma:hidden="true" ma:internalName="MediaServiceEventHashCode" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceObjectDetectorVersions" ma:index="18" nillable="true" ma:displayName="MediaServiceObjectDetectorVersions" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceObjectDetectorVersions" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceDateTaken" ma:index="19" nillable="true" ma:displayName="MediaServiceDateTaken" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceDateTaken" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaLengthInSeconds" ma:index="20" nillable="true" ma:displayName="MediaLengthInSeconds" ma:hidden="true" ma:internalName="MediaLengthInSeconds" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Unknown"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceSearchProperties" ma:index="21" nillable="true" ma:displayName="MediaServiceSearchProperties" ma:hidden="true" ma:internalName="MediaServiceSearchProperties" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="ad65eebb-9aa8-49dc-954e-2f274fb67fdf" elementFormDefault="qualified">
+    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <xsd:element name="TaxCatchAll" ma:index="12" nillable="true" ma:displayName="Taxonomy Catch All Column" ma:hidden="true" ma:list="{6025a312-ae1d-4d43-943f-f94ce9c59120}" ma:internalName="TaxCatchAll" ma:showField="CatchAllData" ma:web="ad65eebb-9aa8-49dc-954e-2f274fb67fdf">
+      <xsd:complexType>
+        <xsd:complexContent>
+          <xsd:extension base="dms:MultiChoiceLookup">
+            <xsd:sequence>
+              <xsd:element name="Value" type="dms:Lookup" maxOccurs="unbounded" minOccurs="0" nillable="true"/>
+            </xsd:sequence>
+          </xsd:extension>
+        </xsd:complexContent>
+      </xsd:complexType>
+    </xsd:element>
+    <xsd:element name="SharedWithUsers" ma:index="16" nillable="true" ma:displayName="Shared With" ma:internalName="SharedWithUsers" ma:readOnly="true">
       <xsd:complexType>
         <xsd:complexContent>
           <xsd:extension base="dms:UserMulti">
@@ -814,57 +886,11 @@
         </xsd:complexContent>
       </xsd:complexType>
     </xsd:element>
-    <xsd:element name="SharingHintHash" ma:index="9" nillable="true" ma:displayName="Sharing Hint Hash" ma:internalName="SharingHintHash" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="SharedWithDetails" ma:index="10" nillable="true" ma:displayName="Shared With Details" ma:internalName="SharedWithDetails" ma:readOnly="true">
+    <xsd:element name="SharedWithDetails" ma:index="17" nillable="true" ma:displayName="Shared With Details" ma:internalName="SharedWithDetails" ma:readOnly="true">
       <xsd:simpleType>
         <xsd:restriction base="dms:Note">
           <xsd:maxLength value="255"/>
         </xsd:restriction>
-      </xsd:simpleType>
-    </xsd:element>
-  </xsd:schema>
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="dcf9c071-f24f-474f-b8f2-caf1c44d8fe8" elementFormDefault="qualified">
-    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <xsd:element name="MediaServiceMetadata" ma:index="11" nillable="true" ma:displayName="MediaServiceMetadata" ma:description="" ma:hidden="true" ma:internalName="MediaServiceMetadata" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceFastMetadata" ma:index="12" nillable="true" ma:displayName="MediaServiceFastMetadata" ma:description="" ma:hidden="true" ma:internalName="MediaServiceFastMetadata" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceAutoTags" ma:index="13" nillable="true" ma:displayName="MediaServiceAutoTags" ma:description="" ma:internalName="MediaServiceAutoTags" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceOCR" ma:index="14" nillable="true" ma:displayName="MediaServiceOCR" ma:internalName="MediaServiceOCR" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note">
-          <xsd:maxLength value="255"/>
-        </xsd:restriction>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceDateTaken" ma:index="15" nillable="true" ma:displayName="MediaServiceDateTaken" ma:hidden="true" ma:internalName="MediaServiceDateTaken" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceEventHashCode" ma:index="16" nillable="true" ma:displayName="MediaServiceEventHashCode" ma:hidden="true" ma:internalName="MediaServiceEventHashCode" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceGenerationTime" ma:index="17" nillable="true" ma:displayName="MediaServiceGenerationTime" ma:hidden="true" ma:internalName="MediaServiceGenerationTime" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
       </xsd:simpleType>
     </xsd:element>
   </xsd:schema>
@@ -978,27 +1004,17 @@
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
+  <documentManagement>
+    <TaxCatchAll xmlns="ad65eebb-9aa8-49dc-954e-2f274fb67fdf" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="347c6671-e14e-499f-bdff-5abebf9f2841">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
 </p:properties>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{34E28598-ABA0-401F-B140-BA0C1D7086C6}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="7183ed49-9f5f-4b04-a53a-40b3f7491946"/>
-    <ds:schemaRef ds:uri="dcf9c071-f24f-474f-b8f2-caf1c44d8fe8"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5910D8B5-3679-49B1-BEE3-C1AAEF9EA1A9}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
